--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104653_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104653_W22.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7411</v>
+        <v>6.1873</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2342</v>
+        <v>1.955</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5068</v>
+        <v>4.2323</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0571</v>
+        <v>4.0567</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7186</v>
+        <v>3.7139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3386</v>
+        <v>0.3428</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3474</v>
+        <v>2.3175</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2484</v>
+        <v>3.2265</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7097</v>
+        <v>1.7391</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4325</v>
+        <v>-0.1182</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0302</v>
+        <v>-0.2652</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4627</v>
+        <v>0.147</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.553</v>
+        <v>4.4186</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5304</v>
+        <v>4.0461</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0226</v>
+        <v>0.3726</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4902</v>
+        <v>3.0237</v>
       </c>
       <c r="H3" t="n">
-        <v>3.586</v>
+        <v>2.5101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0958</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3208</v>
+        <v>3.9232</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3208</v>
+        <v>1.965</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.9582</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1693</v>
+        <v>-0.8995</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2652</v>
+        <v>0.5451</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0958</v>
+        <v>-1.4446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9967</v>
+        <v>0.2568</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3852</v>
+        <v>0.1228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6115</v>
+        <v>0.1339</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.11</v>
+        <v>4.0026</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4777</v>
+        <v>2.3065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6323</v>
+        <v>1.696</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0275</v>
+        <v>3.4911</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5078</v>
+        <v>3.5708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9465</v>
+        <v>3.2848</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9741</v>
+        <v>3.2848</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9724</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9189000000000001</v>
+        <v>0.2063</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5337</v>
+        <v>0.2861</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4526</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0517</v>
+        <v>0.4416</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4688</v>
+        <v>0.2086</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4171</v>
+        <v>0.233</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5987</v>
+        <v>3.9366</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0052</v>
+        <v>3.282</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5936</v>
+        <v>0.6546</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5866</v>
+        <v>4.1932</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6238</v>
+        <v>2.7463</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0372</v>
+        <v>1.447</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1695</v>
+        <v>4.4186</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1695</v>
+        <v>3.2643</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.1543</v>
       </c>
       <c r="M5" t="n">
-        <v>0.417</v>
+        <v>-0.2254</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4542</v>
+        <v>-0.518</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0372</v>
+        <v>0.2926</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.483</v>
+        <v>-0.5816</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2571</v>
+        <v>-0.3627</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2259</v>
+        <v>-0.219</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.356</v>
+        <v>3.5736</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8441</v>
+        <v>1.7194</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5119</v>
+        <v>1.8543</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1904</v>
+        <v>1.5723</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7562</v>
+        <v>1.5956</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4342</v>
+        <v>-0.0232</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4501</v>
+        <v>1.1227</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2933</v>
+        <v>1.1227</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1568</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2597</v>
+        <v>0.4497</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5371</v>
+        <v>0.4729</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2773</v>
+        <v>-0.0232</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1442</v>
+        <v>-0.5027</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>-0.4928</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3094</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7712</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4141</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.623</v>
+        <v>1.0406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8679</v>
+        <v>1.2135</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.245</v>
+        <v>-0.173</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.581</v>
+        <v>-0.5785</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4184</v>
+        <v>-0.4193</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1626</v>
+        <v>-0.1592</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0856</v>
+        <v>-0.0919</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5692</v>
+        <v>-0.1533</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5475</v>
+        <v>0.3199</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1765</v>
+        <v>1.8076</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6291</v>
+        <v>-1.4877</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1184</v>
+        <v>0.2448</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.153</v>
+        <v>-1.522</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0346</v>
+        <v>1.7668</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4597</v>
+        <v>2.5493</v>
       </c>
       <c r="K8" t="n">
-        <v>0.052</v>
+        <v>-0.8316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4078</v>
+        <v>3.3809</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-2.3045</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.205</v>
+        <v>-0.6904</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3732</v>
+        <v>-1.6141</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7585</v>
+        <v>-0.9233</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7168</v>
+        <v>0.0809</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0417</v>
+        <v>-1.0042</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8416</v>
+        <v>0.2597</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0257</v>
+        <v>0.8182</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8673</v>
+        <v>-0.5585</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2467</v>
+        <v>-0.12</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5179</v>
+        <v>-0.1495</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7646</v>
+        <v>0.0296</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5854</v>
+        <v>0.4536</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8077</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3931</v>
+        <v>0.4019</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3388</v>
+        <v>-0.5736</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7103</v>
+        <v>-0.2012</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6285</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0902</v>
+        <v>0.4692</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.747</v>
+        <v>0.3646</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3432</v>
+        <v>0.1046</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1151</v>
+        <v>-1.3646</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0553</v>
+        <v>0.7008</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1704</v>
+        <v>-2.0654</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2321</v>
+        <v>-1.2217</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0029</v>
+        <v>-0.9969</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2292</v>
+        <v>-0.2247</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6863</v>
+        <v>0.6847</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9185</v>
+        <v>-1.9064</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0549</v>
+        <v>-1.0487</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1171</v>
+        <v>-0.1429</v>
       </c>
       <c r="T10" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2956</v>
+        <v>-2.0512</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6435</v>
+        <v>-2.4551</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3478</v>
+        <v>0.4039</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4315</v>
+        <v>-0.4127</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8369</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3177</v>
+        <v>1.2874</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7491</v>
+        <v>-1.7001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3179</v>
+        <v>-0.2888</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4312</v>
+        <v>-1.4113</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8227</v>
+        <v>-0.5898</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5172</v>
+        <v>-0.2793</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3055</v>
+        <v>-0.3105</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5576</v>
+        <v>-2.4768</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6356</v>
+        <v>-1.5364</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.922</v>
+        <v>-0.9405</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1742</v>
+        <v>-1.1758</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.049</v>
+        <v>-1.0538</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1253</v>
+        <v>-0.122</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3325</v>
+        <v>-0.3444</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4818</v>
+        <v>-0.4934</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3173</v>
+        <v>-0.2312</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0124</v>
+        <v>-0.0196</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9956</v>
+        <v>-3.1013</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7484</v>
+        <v>-0.9974</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2472</v>
+        <v>-2.1039</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5641</v>
+        <v>-2.5646</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6391</v>
+        <v>-1.6426</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6637</v>
+        <v>-1.6767</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9147</v>
+        <v>-0.9243</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9003</v>
+        <v>-0.8879</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0194</v>
+        <v>-0.1301</v>
       </c>
       <c r="T13" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7238</v>
+        <v>14.745</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1895</v>
+        <v>12.8602</v>
       </c>
       <c r="F14" t="n">
-        <v>1.534000000000001</v>
+        <v>1.884700000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>10.4972</v>
+        <v>10.5085</v>
       </c>
       <c r="H14" t="n">
-        <v>8.817499999999999</v>
+        <v>8.762999999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6798</v>
+        <v>1.746</v>
       </c>
       <c r="J14" t="n">
-        <v>18.2016</v>
+        <v>17.9288</v>
       </c>
       <c r="K14" t="n">
-        <v>11.4316</v>
+        <v>11.213</v>
       </c>
       <c r="L14" t="n">
-        <v>6.770200000000001</v>
+        <v>6.7156</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.7045</v>
+        <v>-7.4203</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6146</v>
+        <v>-2.4502</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.0901</v>
+        <v>-4.970200000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>6.805100000000001</v>
+        <v>6.8289</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3417</v>
+        <v>-11.3816</v>
       </c>
       <c r="R14" t="n">
-        <v>18.1469</v>
+        <v>18.2105</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1929</v>
+        <v>-2.2055</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4838</v>
+        <v>-0.4681</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7089</v>
+        <v>-1.7376</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3855999999999999</v>
+        <v>-0.3870000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8133</v>
+        <v>6.781</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.198800000000001</v>
+        <v>-7.1678</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5855</v>
+        <v>3.9667</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5576</v>
+        <v>4.5502</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9721</v>
+        <v>-0.5834</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0054</v>
+        <v>2.9829</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5019</v>
+        <v>2.5152</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4676</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2636</v>
+        <v>5.2044</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3075</v>
+        <v>3.2922</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9561</v>
+        <v>1.9122</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2583</v>
+        <v>-2.2216</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8056</v>
+        <v>-0.777</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6713</v>
+        <v>-0.2649</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0767</v>
+        <v>-0.0122</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5946</v>
+        <v>-0.2527</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8704</v>
+        <v>1.6502</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1253</v>
+        <v>4.4221</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2549</v>
+        <v>-2.7719</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7855</v>
+        <v>2.7825</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4709</v>
+        <v>2.4666</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0169</v>
+        <v>4.9764</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6238</v>
+        <v>1.5956</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3931</v>
+        <v>3.3809</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2314</v>
+        <v>-2.194</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3092</v>
+        <v>-1.2797</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.3717</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2208</v>
+        <v>0.1365</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8008</v>
+        <v>0.2352</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3953</v>
+        <v>0.2043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7844</v>
+        <v>1.2306</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.389</v>
+        <v>-1.0263</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3511</v>
+        <v>-0.8802</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0606</v>
+        <v>-1.7353</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2905</v>
+        <v>0.8551</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2803</v>
+        <v>1.3298</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7682</v>
+        <v>-0.0107</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4878</v>
+        <v>1.3405</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6314</v>
+        <v>-2.21</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8287</v>
+        <v>-1.7246</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1973</v>
+        <v>-0.4854</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8806</v>
+        <v>1.0845</v>
       </c>
       <c r="T17" t="n">
-        <v>2.226</v>
+        <v>0.4943</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3454</v>
+        <v>0.5903</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2579</v>
+        <v>-0.159</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6025</v>
+        <v>0.2296</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3446</v>
+        <v>-0.3886</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8932</v>
+        <v>-1.7458</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7461</v>
+        <v>-1.5173</v>
       </c>
       <c r="I18" t="n">
-        <v>0.853</v>
+        <v>-0.2285</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3465</v>
+        <v>0.1929</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0031</v>
+        <v>0.7822</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3434</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2397</v>
+        <v>-1.9387</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7493</v>
+        <v>-2.2995</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4904</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1511</v>
+        <v>0.1299</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8438</v>
+        <v>0.0853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3073</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5849</v>
+        <v>-0.4048</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.4325</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5003</v>
+        <v>0.0277</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7487</v>
+        <v>-1.3488</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5327</v>
+        <v>-1.0598</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.216</v>
+        <v>-0.2889</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2291</v>
+        <v>0.2452</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7997</v>
+        <v>0.737</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5706</v>
+        <v>-0.4917</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9778</v>
+        <v>-1.594</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3323</v>
+        <v>-1.7968</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3546</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2879</v>
+        <v>1.0821</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2722</v>
+        <v>1.0538</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0157</v>
+        <v>0.0283</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7712</v>
+        <v>0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0745</v>
+        <v>-2.9339</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8812</v>
+        <v>-1.0146</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1933</v>
+        <v>-1.9193</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5575</v>
+        <v>-1.5528</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.267</v>
+        <v>-1.2639</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2905</v>
+        <v>-0.2889</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2949</v>
+        <v>-0.3057</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9666</v>
+        <v>-0.976</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2626</v>
+        <v>-1.2471</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.483</v>
+        <v>0.6189</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0959</v>
+        <v>0.3474</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3825</v>
+        <v>-3.9233</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0926</v>
+        <v>-1.7688</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2899</v>
+        <v>-2.1545</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0824</v>
+        <v>-4.0836</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2671</v>
+        <v>-2.2552</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8153</v>
+        <v>-1.8283</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7145</v>
+        <v>-1.7474</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6664</v>
+        <v>-1.6795</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0481</v>
+        <v>-0.0679</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3679</v>
+        <v>-2.3362</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6007</v>
+        <v>-0.5758</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6345</v>
+        <v>-0.186</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.378</v>
+        <v>-0.0214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2565</v>
+        <v>-0.1645</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.494</v>
+        <v>-5.6381</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9527</v>
+        <v>-5.1223</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5414</v>
+        <v>-0.5158</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7956</v>
+        <v>-1.8049</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1876</v>
+        <v>0.184</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9832</v>
+        <v>-1.9889</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1231</v>
+        <v>-0.1553</v>
       </c>
       <c r="K22" t="n">
-        <v>1.527</v>
+        <v>1.5061</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6725</v>
+        <v>-1.6496</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5414</v>
+        <v>0.425</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2971</v>
+        <v>-6.7174</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6856</v>
+        <v>-5.0683</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6114</v>
+        <v>-1.6491</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.8596</v>
+        <v>-4.858</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9479</v>
+        <v>-3.9463</v>
       </c>
       <c r="I23" t="n">
         <v>-0.9116</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2994</v>
+        <v>-2.3202</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.7818</v>
+        <v>-2.7966</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5602</v>
+        <v>-2.5378</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1503</v>
+        <v>-0.266</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1179</v>
+        <v>-0.4718</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2683</v>
+        <v>0.2058</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.7239</v>
+        <v>-13.9553</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6269</v>
+        <v>-2.973999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.0969</v>
+        <v>-10.9812</v>
       </c>
       <c r="G24" t="n">
-        <v>-10.4972</v>
+        <v>-10.5087</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.817400000000001</v>
+        <v>-8.762699999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6797</v>
+        <v>-1.7458</v>
       </c>
       <c r="J24" t="n">
-        <v>7.704499999999999</v>
+        <v>7.4201</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6145</v>
+        <v>2.450299999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>5.0901</v>
+        <v>4.9701</v>
       </c>
       <c r="M24" t="n">
-        <v>-18.2018</v>
+        <v>-17.929</v>
       </c>
       <c r="N24" t="n">
-        <v>-11.4316</v>
+        <v>-11.2131</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.7698</v>
+        <v>-6.7159</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.8049</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q24" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R24" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1928</v>
+        <v>2.9952</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7089</v>
+        <v>1.7378</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4838999999999999</v>
+        <v>1.2576</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3855</v>
+        <v>0.3868</v>
       </c>
       <c r="W24" t="n">
-        <v>6.1062</v>
+        <v>6.078399999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.720499999999999</v>
+        <v>-5.6913</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104653_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104653_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.1678</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104653_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-5.6913</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
